--- a/virtual-physics-lab/app/dl/NJC_Q2b_cooling_dataset.xlsx
+++ b/virtual-physics-lab/app/dl/NJC_Q2b_cooling_dataset.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +100,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -668,550 +669,550 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>87.97</v>
-      </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="B6" s="6" t="n">
+        <v>88.06999999999999</v>
+      </c>
+      <c r="C6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>86.14</v>
-      </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="B7" s="6" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="C7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>84.52</v>
-      </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="B8" s="6" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="C8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="C9" s="6" t="n"/>
+      <c r="B9" s="6" t="n">
+        <v>82.83</v>
+      </c>
+      <c r="C9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="C10" s="6" t="n"/>
+      <c r="B10" s="6" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="C10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>79.48999999999999</v>
-      </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="B11" s="6" t="n">
+        <v>79.48</v>
+      </c>
+      <c r="C11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>78.14</v>
-      </c>
-      <c r="C12" s="6" t="n"/>
+      <c r="B12" s="6" t="n">
+        <v>77.95999999999999</v>
+      </c>
+      <c r="C12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>76.53</v>
-      </c>
-      <c r="C13" s="6" t="n"/>
+      <c r="B13" s="6" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="C13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
         <v>240</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>75.23999999999999</v>
-      </c>
-      <c r="C14" s="6" t="n"/>
+      <c r="B14" s="6" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="C14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
         <v>270</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>73.67</v>
-      </c>
-      <c r="C15" s="6" t="n"/>
+      <c r="B15" s="6" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="C15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="C16" s="6" t="n"/>
+      <c r="B16" s="6" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="C16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
         <v>330</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>71.06</v>
-      </c>
-      <c r="C17" s="6" t="n"/>
+      <c r="B17" s="6" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="C17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>69.75</v>
-      </c>
-      <c r="C18" s="6" t="n"/>
+      <c r="B18" s="6" t="n">
+        <v>69.79000000000001</v>
+      </c>
+      <c r="C18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
         <v>390</v>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>68.41</v>
-      </c>
-      <c r="C19" s="6" t="n"/>
+      <c r="B19" s="6" t="n">
+        <v>68.52</v>
+      </c>
+      <c r="C19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
         <v>420</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>67.27</v>
-      </c>
-      <c r="C20" s="6" t="n"/>
+      <c r="B20" s="6" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="C20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
         <v>450</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>66.06</v>
-      </c>
-      <c r="C21" s="6" t="n"/>
+      <c r="B21" s="6" t="n">
+        <v>66.11</v>
+      </c>
+      <c r="C21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
         <v>480</v>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>65.11</v>
-      </c>
-      <c r="C22" s="6" t="n"/>
+      <c r="B22" s="6" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="C22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
         <v>510</v>
       </c>
-      <c r="B23" s="5" t="n">
-        <v>63.99</v>
-      </c>
-      <c r="C23" s="6" t="n"/>
+      <c r="B23" s="6" t="n">
+        <v>64.03</v>
+      </c>
+      <c r="C23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
         <v>540</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>63.06</v>
-      </c>
-      <c r="C24" s="6" t="n"/>
+      <c r="B24" s="6" t="n">
+        <v>62.94</v>
+      </c>
+      <c r="C24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
         <v>570</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>61.93</v>
-      </c>
-      <c r="C25" s="6" t="n"/>
+      <c r="B25" s="6" t="n">
+        <v>62.04</v>
+      </c>
+      <c r="C25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="C26" s="6" t="n"/>
+      <c r="B26" s="6" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="C26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
         <v>630</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>60.04</v>
-      </c>
-      <c r="C27" s="6" t="n"/>
+      <c r="B27" s="6" t="n">
+        <v>59.95</v>
+      </c>
+      <c r="C27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
         <v>660</v>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>58.97</v>
-      </c>
-      <c r="C28" s="6" t="n"/>
+      <c r="B28" s="6" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="C28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
         <v>690</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="C29" s="6" t="n"/>
+      <c r="B29" s="6" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="C29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>57.28</v>
-      </c>
-      <c r="C30" s="6" t="n"/>
+      <c r="B30" s="6" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="C30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
         <v>750</v>
       </c>
-      <c r="B31" s="5" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="C31" s="6" t="n"/>
+      <c r="B31" s="6" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="C31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
         <v>780</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>55.54</v>
-      </c>
-      <c r="C32" s="6" t="n"/>
+      <c r="B32" s="6" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="C32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
         <v>810</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>54.69</v>
-      </c>
-      <c r="C33" s="6" t="n"/>
+      <c r="B33" s="6" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="C33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
         <v>840</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>53.97</v>
-      </c>
-      <c r="C34" s="6" t="n"/>
+      <c r="B34" s="6" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="C34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
         <v>870</v>
       </c>
-      <c r="B35" s="5" t="n">
-        <v>53.29</v>
-      </c>
-      <c r="C35" s="6" t="n"/>
+      <c r="B35" s="6" t="n">
+        <v>53.22</v>
+      </c>
+      <c r="C35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
         <v>900</v>
       </c>
-      <c r="B36" s="5" t="n">
-        <v>52.59</v>
-      </c>
-      <c r="C36" s="6" t="n"/>
+      <c r="B36" s="6" t="n">
+        <v>52.57</v>
+      </c>
+      <c r="C36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
         <v>930</v>
       </c>
-      <c r="B37" s="5" t="n">
-        <v>51.83</v>
-      </c>
-      <c r="C37" s="6" t="n"/>
+      <c r="B37" s="6" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="C37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
         <v>960</v>
       </c>
-      <c r="B38" s="5" t="n">
-        <v>51.21</v>
-      </c>
-      <c r="C38" s="6" t="n"/>
+      <c r="B38" s="6" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="C38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
         <v>990</v>
       </c>
-      <c r="B39" s="5" t="n">
-        <v>50.61</v>
-      </c>
-      <c r="C39" s="6" t="n"/>
+      <c r="B39" s="6" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="C39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
         <v>1020</v>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="6" t="n">
         <v>49.98</v>
       </c>
-      <c r="C40" s="6" t="n"/>
+      <c r="C40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
         <v>1050</v>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="6" t="n">
         <v>49.36</v>
       </c>
-      <c r="C41" s="6" t="n"/>
+      <c r="C41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
         <v>1080</v>
       </c>
-      <c r="B42" s="5" t="n">
-        <v>48.72</v>
-      </c>
-      <c r="C42" s="6" t="n"/>
+      <c r="B42" s="6" t="n">
+        <v>48.76</v>
+      </c>
+      <c r="C42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
         <v>1110</v>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>48.04</v>
-      </c>
-      <c r="C43" s="6" t="n"/>
+      <c r="B43" s="6" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="C43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
         <v>1140</v>
       </c>
-      <c r="B44" s="5" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="C44" s="6" t="n"/>
+      <c r="B44" s="6" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="C44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
         <v>1170</v>
       </c>
-      <c r="B45" s="5" t="n">
-        <v>47.04</v>
-      </c>
-      <c r="C45" s="6" t="n"/>
+      <c r="B45" s="6" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="C45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="B46" s="5" t="n">
-        <v>46.48</v>
-      </c>
-      <c r="C46" s="6" t="n"/>
+      <c r="B46" s="6" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="C46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
         <v>1230</v>
       </c>
-      <c r="B47" s="5" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="C47" s="6" t="n"/>
+      <c r="B47" s="6" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="C47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
         <v>1260</v>
       </c>
-      <c r="B48" s="5" t="n">
-        <v>45.45</v>
-      </c>
-      <c r="C48" s="6" t="n"/>
+      <c r="B48" s="6" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="C48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
         <v>1290</v>
       </c>
-      <c r="B49" s="5" t="n">
-        <v>44.95</v>
-      </c>
-      <c r="C49" s="6" t="n"/>
+      <c r="B49" s="6" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="C49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
         <v>1320</v>
       </c>
-      <c r="B50" s="5" t="n">
-        <v>44.42</v>
-      </c>
-      <c r="C50" s="6" t="n"/>
+      <c r="B50" s="6" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="C50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
         <v>1350</v>
       </c>
-      <c r="B51" s="5" t="n">
-        <v>44.11</v>
-      </c>
-      <c r="C51" s="6" t="n"/>
+      <c r="B51" s="6" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="C51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
         <v>1380</v>
       </c>
-      <c r="B52" s="5" t="n">
-        <v>43.55</v>
-      </c>
-      <c r="C52" s="6" t="n"/>
+      <c r="B52" s="6" t="n">
+        <v>43.67</v>
+      </c>
+      <c r="C52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
         <v>1410</v>
       </c>
-      <c r="B53" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="C53" s="6" t="n"/>
+      <c r="B53" s="6" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="C53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
         <v>1440</v>
       </c>
-      <c r="B54" s="5" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="C54" s="6" t="n"/>
+      <c r="B54" s="6" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="C54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
         <v>1470</v>
       </c>
-      <c r="B55" s="5" t="n">
-        <v>42.39</v>
-      </c>
-      <c r="C55" s="6" t="n"/>
+      <c r="B55" s="6" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="C55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="C56" s="6" t="n"/>
+      <c r="C56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
         <v>1530</v>
       </c>
-      <c r="B57" s="5" t="n">
-        <v>41.55</v>
-      </c>
-      <c r="C57" s="6" t="n"/>
+      <c r="B57" s="6" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="C57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
         <v>1560</v>
       </c>
-      <c r="B58" s="5" t="n">
-        <v>41.23</v>
-      </c>
-      <c r="C58" s="6" t="n"/>
+      <c r="B58" s="6" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="C58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
         <v>1590</v>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="6" t="n">
         <v>40.88</v>
       </c>
-      <c r="C59" s="6" t="n"/>
+      <c r="C59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
         <v>1620</v>
       </c>
-      <c r="B60" s="5" t="n">
-        <v>40.62</v>
-      </c>
-      <c r="C60" s="6" t="n"/>
+      <c r="B60" s="6" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="C60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="B61" s="5" t="n">
-        <v>40.32</v>
-      </c>
-      <c r="C61" s="6" t="n"/>
+      <c r="B61" s="6" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="C61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
         <v>1680</v>
       </c>
-      <c r="B62" s="5" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="C62" s="6" t="n"/>
+      <c r="B62" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="C62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
         <v>1710</v>
       </c>
-      <c r="B63" s="5" t="n">
-        <v>39.59</v>
-      </c>
-      <c r="C63" s="6" t="n"/>
+      <c r="B63" s="6" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="C63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
         <v>1740</v>
       </c>
-      <c r="B64" s="5" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="C64" s="6" t="n"/>
+      <c r="B64" s="6" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="C64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
         <v>1770</v>
       </c>
-      <c r="B65" s="5" t="n">
-        <v>39.13</v>
-      </c>
-      <c r="C65" s="6" t="n"/>
+      <c r="B65" s="6" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="C65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
         <v>1800</v>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="6" t="n">
         <v>38.85</v>
       </c>
-      <c r="C66" s="6" t="n"/>
+      <c r="C66" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1285,10 +1286,10 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>87.97</v>
-      </c>
-      <c r="C6" s="7">
+      <c r="B6" s="6" t="n">
+        <v>88.06999999999999</v>
+      </c>
+      <c r="C6" s="8">
         <f>LN(B6-30)</f>
         <v/>
       </c>
@@ -1297,7 +1298,7 @@
           <t>gradient</t>
         </is>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>SLOPE(C6:C66,A6:A66)</f>
         <v/>
       </c>
@@ -1311,10 +1312,10 @@
       <c r="A7" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>86.14</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="B7" s="6" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="C7" s="8">
         <f>LN(B7-30)</f>
         <v/>
       </c>
@@ -1323,7 +1324,7 @@
           <t>k = −gradient</t>
         </is>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f>-SLOPE(C6:C66,A6:A66)</f>
         <v/>
       </c>
@@ -1337,10 +1338,10 @@
       <c r="A8" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>84.52</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="B8" s="6" t="n">
+        <v>84.39</v>
+      </c>
+      <c r="C8" s="8">
         <f>LN(B8-30)</f>
         <v/>
       </c>
@@ -1349,7 +1350,7 @@
           <t>n = e^intercept</t>
         </is>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f>EXP(INTERCEPT(C6:C66,A6:A66))</f>
         <v/>
       </c>
@@ -1363,10 +1364,10 @@
       <c r="A9" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B9" s="5" t="n">
-        <v>82.67</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="B9" s="6" t="n">
+        <v>82.83</v>
+      </c>
+      <c r="C9" s="8">
         <f>LN(B9-30)</f>
         <v/>
       </c>
@@ -1375,10 +1376,10 @@
       <c r="A10" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B10" s="6" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="C10" s="8">
         <f>LN(B10-30)</f>
         <v/>
       </c>
@@ -1387,10 +1388,10 @@
       <c r="A11" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>79.48999999999999</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="B11" s="6" t="n">
+        <v>79.48</v>
+      </c>
+      <c r="C11" s="8">
         <f>LN(B11-30)</f>
         <v/>
       </c>
@@ -1399,10 +1400,10 @@
       <c r="A12" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>78.14</v>
-      </c>
-      <c r="C12" s="7">
+      <c r="B12" s="6" t="n">
+        <v>77.95999999999999</v>
+      </c>
+      <c r="C12" s="8">
         <f>LN(B12-30)</f>
         <v/>
       </c>
@@ -1411,10 +1412,10 @@
       <c r="A13" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>76.53</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="B13" s="6" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="C13" s="8">
         <f>LN(B13-30)</f>
         <v/>
       </c>
@@ -1423,10 +1424,10 @@
       <c r="A14" s="5" t="n">
         <v>240</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>75.23999999999999</v>
-      </c>
-      <c r="C14" s="7">
+      <c r="B14" s="6" t="n">
+        <v>75.09</v>
+      </c>
+      <c r="C14" s="8">
         <f>LN(B14-30)</f>
         <v/>
       </c>
@@ -1435,10 +1436,10 @@
       <c r="A15" s="5" t="n">
         <v>270</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>73.67</v>
-      </c>
-      <c r="C15" s="7">
+      <c r="B15" s="6" t="n">
+        <v>73.84</v>
+      </c>
+      <c r="C15" s="8">
         <f>LN(B15-30)</f>
         <v/>
       </c>
@@ -1447,10 +1448,10 @@
       <c r="A16" s="5" t="n">
         <v>300</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="C16" s="7">
+      <c r="B16" s="6" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="C16" s="8">
         <f>LN(B16-30)</f>
         <v/>
       </c>
@@ -1459,10 +1460,10 @@
       <c r="A17" s="5" t="n">
         <v>330</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>71.06</v>
-      </c>
-      <c r="C17" s="7">
+      <c r="B17" s="6" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="C17" s="8">
         <f>LN(B17-30)</f>
         <v/>
       </c>
@@ -1471,10 +1472,10 @@
       <c r="A18" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>69.75</v>
-      </c>
-      <c r="C18" s="7">
+      <c r="B18" s="6" t="n">
+        <v>69.79000000000001</v>
+      </c>
+      <c r="C18" s="8">
         <f>LN(B18-30)</f>
         <v/>
       </c>
@@ -1483,10 +1484,10 @@
       <c r="A19" s="5" t="n">
         <v>390</v>
       </c>
-      <c r="B19" s="5" t="n">
-        <v>68.41</v>
-      </c>
-      <c r="C19" s="7">
+      <c r="B19" s="6" t="n">
+        <v>68.52</v>
+      </c>
+      <c r="C19" s="8">
         <f>LN(B19-30)</f>
         <v/>
       </c>
@@ -1495,10 +1496,10 @@
       <c r="A20" s="5" t="n">
         <v>420</v>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>67.27</v>
-      </c>
-      <c r="C20" s="7">
+      <c r="B20" s="6" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="C20" s="8">
         <f>LN(B20-30)</f>
         <v/>
       </c>
@@ -1507,10 +1508,10 @@
       <c r="A21" s="5" t="n">
         <v>450</v>
       </c>
-      <c r="B21" s="5" t="n">
-        <v>66.06</v>
-      </c>
-      <c r="C21" s="7">
+      <c r="B21" s="6" t="n">
+        <v>66.11</v>
+      </c>
+      <c r="C21" s="8">
         <f>LN(B21-30)</f>
         <v/>
       </c>
@@ -1519,10 +1520,10 @@
       <c r="A22" s="5" t="n">
         <v>480</v>
       </c>
-      <c r="B22" s="5" t="n">
-        <v>65.11</v>
-      </c>
-      <c r="C22" s="7">
+      <c r="B22" s="6" t="n">
+        <v>64.94</v>
+      </c>
+      <c r="C22" s="8">
         <f>LN(B22-30)</f>
         <v/>
       </c>
@@ -1531,10 +1532,10 @@
       <c r="A23" s="5" t="n">
         <v>510</v>
       </c>
-      <c r="B23" s="5" t="n">
-        <v>63.99</v>
-      </c>
-      <c r="C23" s="7">
+      <c r="B23" s="6" t="n">
+        <v>64.03</v>
+      </c>
+      <c r="C23" s="8">
         <f>LN(B23-30)</f>
         <v/>
       </c>
@@ -1543,10 +1544,10 @@
       <c r="A24" s="5" t="n">
         <v>540</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>63.06</v>
-      </c>
-      <c r="C24" s="7">
+      <c r="B24" s="6" t="n">
+        <v>62.94</v>
+      </c>
+      <c r="C24" s="8">
         <f>LN(B24-30)</f>
         <v/>
       </c>
@@ -1555,10 +1556,10 @@
       <c r="A25" s="5" t="n">
         <v>570</v>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>61.93</v>
-      </c>
-      <c r="C25" s="7">
+      <c r="B25" s="6" t="n">
+        <v>62.04</v>
+      </c>
+      <c r="C25" s="8">
         <f>LN(B25-30)</f>
         <v/>
       </c>
@@ -1567,10 +1568,10 @@
       <c r="A26" s="5" t="n">
         <v>600</v>
       </c>
-      <c r="B26" s="5" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="C26" s="7">
+      <c r="B26" s="6" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="C26" s="8">
         <f>LN(B26-30)</f>
         <v/>
       </c>
@@ -1579,10 +1580,10 @@
       <c r="A27" s="5" t="n">
         <v>630</v>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>60.04</v>
-      </c>
-      <c r="C27" s="7">
+      <c r="B27" s="6" t="n">
+        <v>59.95</v>
+      </c>
+      <c r="C27" s="8">
         <f>LN(B27-30)</f>
         <v/>
       </c>
@@ -1591,10 +1592,10 @@
       <c r="A28" s="5" t="n">
         <v>660</v>
       </c>
-      <c r="B28" s="5" t="n">
-        <v>58.97</v>
-      </c>
-      <c r="C28" s="7">
+      <c r="B28" s="6" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="C28" s="8">
         <f>LN(B28-30)</f>
         <v/>
       </c>
@@ -1603,10 +1604,10 @@
       <c r="A29" s="5" t="n">
         <v>690</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="C29" s="7">
+      <c r="B29" s="6" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="C29" s="8">
         <f>LN(B29-30)</f>
         <v/>
       </c>
@@ -1615,10 +1616,10 @@
       <c r="A30" s="5" t="n">
         <v>720</v>
       </c>
-      <c r="B30" s="5" t="n">
-        <v>57.28</v>
-      </c>
-      <c r="C30" s="7">
+      <c r="B30" s="6" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="C30" s="8">
         <f>LN(B30-30)</f>
         <v/>
       </c>
@@ -1627,10 +1628,10 @@
       <c r="A31" s="5" t="n">
         <v>750</v>
       </c>
-      <c r="B31" s="5" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="C31" s="7">
+      <c r="B31" s="6" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="C31" s="8">
         <f>LN(B31-30)</f>
         <v/>
       </c>
@@ -1639,10 +1640,10 @@
       <c r="A32" s="5" t="n">
         <v>780</v>
       </c>
-      <c r="B32" s="5" t="n">
-        <v>55.54</v>
-      </c>
-      <c r="C32" s="7">
+      <c r="B32" s="6" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="C32" s="8">
         <f>LN(B32-30)</f>
         <v/>
       </c>
@@ -1651,10 +1652,10 @@
       <c r="A33" s="5" t="n">
         <v>810</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>54.69</v>
-      </c>
-      <c r="C33" s="7">
+      <c r="B33" s="6" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="C33" s="8">
         <f>LN(B33-30)</f>
         <v/>
       </c>
@@ -1663,10 +1664,10 @@
       <c r="A34" s="5" t="n">
         <v>840</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>53.97</v>
-      </c>
-      <c r="C34" s="7">
+      <c r="B34" s="6" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="C34" s="8">
         <f>LN(B34-30)</f>
         <v/>
       </c>
@@ -1675,10 +1676,10 @@
       <c r="A35" s="5" t="n">
         <v>870</v>
       </c>
-      <c r="B35" s="5" t="n">
-        <v>53.29</v>
-      </c>
-      <c r="C35" s="7">
+      <c r="B35" s="6" t="n">
+        <v>53.22</v>
+      </c>
+      <c r="C35" s="8">
         <f>LN(B35-30)</f>
         <v/>
       </c>
@@ -1687,10 +1688,10 @@
       <c r="A36" s="5" t="n">
         <v>900</v>
       </c>
-      <c r="B36" s="5" t="n">
-        <v>52.59</v>
-      </c>
-      <c r="C36" s="7">
+      <c r="B36" s="6" t="n">
+        <v>52.57</v>
+      </c>
+      <c r="C36" s="8">
         <f>LN(B36-30)</f>
         <v/>
       </c>
@@ -1699,10 +1700,10 @@
       <c r="A37" s="5" t="n">
         <v>930</v>
       </c>
-      <c r="B37" s="5" t="n">
-        <v>51.83</v>
-      </c>
-      <c r="C37" s="7">
+      <c r="B37" s="6" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="C37" s="8">
         <f>LN(B37-30)</f>
         <v/>
       </c>
@@ -1711,10 +1712,10 @@
       <c r="A38" s="5" t="n">
         <v>960</v>
       </c>
-      <c r="B38" s="5" t="n">
-        <v>51.21</v>
-      </c>
-      <c r="C38" s="7">
+      <c r="B38" s="6" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="C38" s="8">
         <f>LN(B38-30)</f>
         <v/>
       </c>
@@ -1723,10 +1724,10 @@
       <c r="A39" s="5" t="n">
         <v>990</v>
       </c>
-      <c r="B39" s="5" t="n">
-        <v>50.61</v>
-      </c>
-      <c r="C39" s="7">
+      <c r="B39" s="6" t="n">
+        <v>50.55</v>
+      </c>
+      <c r="C39" s="8">
         <f>LN(B39-30)</f>
         <v/>
       </c>
@@ -1735,10 +1736,10 @@
       <c r="A40" s="5" t="n">
         <v>1020</v>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="6" t="n">
         <v>49.98</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="8">
         <f>LN(B40-30)</f>
         <v/>
       </c>
@@ -1747,10 +1748,10 @@
       <c r="A41" s="5" t="n">
         <v>1050</v>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="6" t="n">
         <v>49.36</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="8">
         <f>LN(B41-30)</f>
         <v/>
       </c>
@@ -1759,10 +1760,10 @@
       <c r="A42" s="5" t="n">
         <v>1080</v>
       </c>
-      <c r="B42" s="5" t="n">
-        <v>48.72</v>
-      </c>
-      <c r="C42" s="7">
+      <c r="B42" s="6" t="n">
+        <v>48.76</v>
+      </c>
+      <c r="C42" s="8">
         <f>LN(B42-30)</f>
         <v/>
       </c>
@@ -1771,10 +1772,10 @@
       <c r="A43" s="5" t="n">
         <v>1110</v>
       </c>
-      <c r="B43" s="5" t="n">
-        <v>48.04</v>
-      </c>
-      <c r="C43" s="7">
+      <c r="B43" s="6" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="C43" s="8">
         <f>LN(B43-30)</f>
         <v/>
       </c>
@@ -1783,10 +1784,10 @@
       <c r="A44" s="5" t="n">
         <v>1140</v>
       </c>
-      <c r="B44" s="5" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="C44" s="7">
+      <c r="B44" s="6" t="n">
+        <v>47.48</v>
+      </c>
+      <c r="C44" s="8">
         <f>LN(B44-30)</f>
         <v/>
       </c>
@@ -1795,10 +1796,10 @@
       <c r="A45" s="5" t="n">
         <v>1170</v>
       </c>
-      <c r="B45" s="5" t="n">
-        <v>47.04</v>
-      </c>
-      <c r="C45" s="7">
+      <c r="B45" s="6" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="C45" s="8">
         <f>LN(B45-30)</f>
         <v/>
       </c>
@@ -1807,10 +1808,10 @@
       <c r="A46" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="B46" s="5" t="n">
-        <v>46.48</v>
-      </c>
-      <c r="C46" s="7">
+      <c r="B46" s="6" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="C46" s="8">
         <f>LN(B46-30)</f>
         <v/>
       </c>
@@ -1819,10 +1820,10 @@
       <c r="A47" s="5" t="n">
         <v>1230</v>
       </c>
-      <c r="B47" s="5" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="C47" s="7">
+      <c r="B47" s="6" t="n">
+        <v>45.97</v>
+      </c>
+      <c r="C47" s="8">
         <f>LN(B47-30)</f>
         <v/>
       </c>
@@ -1831,10 +1832,10 @@
       <c r="A48" s="5" t="n">
         <v>1260</v>
       </c>
-      <c r="B48" s="5" t="n">
-        <v>45.45</v>
-      </c>
-      <c r="C48" s="7">
+      <c r="B48" s="6" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="C48" s="8">
         <f>LN(B48-30)</f>
         <v/>
       </c>
@@ -1843,10 +1844,10 @@
       <c r="A49" s="5" t="n">
         <v>1290</v>
       </c>
-      <c r="B49" s="5" t="n">
-        <v>44.95</v>
-      </c>
-      <c r="C49" s="7">
+      <c r="B49" s="6" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="C49" s="8">
         <f>LN(B49-30)</f>
         <v/>
       </c>
@@ -1855,10 +1856,10 @@
       <c r="A50" s="5" t="n">
         <v>1320</v>
       </c>
-      <c r="B50" s="5" t="n">
-        <v>44.42</v>
-      </c>
-      <c r="C50" s="7">
+      <c r="B50" s="6" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="C50" s="8">
         <f>LN(B50-30)</f>
         <v/>
       </c>
@@ -1867,10 +1868,10 @@
       <c r="A51" s="5" t="n">
         <v>1350</v>
       </c>
-      <c r="B51" s="5" t="n">
-        <v>44.11</v>
-      </c>
-      <c r="C51" s="7">
+      <c r="B51" s="6" t="n">
+        <v>43.97</v>
+      </c>
+      <c r="C51" s="8">
         <f>LN(B51-30)</f>
         <v/>
       </c>
@@ -1879,10 +1880,10 @@
       <c r="A52" s="5" t="n">
         <v>1380</v>
       </c>
-      <c r="B52" s="5" t="n">
-        <v>43.55</v>
-      </c>
-      <c r="C52" s="7">
+      <c r="B52" s="6" t="n">
+        <v>43.67</v>
+      </c>
+      <c r="C52" s="8">
         <f>LN(B52-30)</f>
         <v/>
       </c>
@@ -1891,10 +1892,10 @@
       <c r="A53" s="5" t="n">
         <v>1410</v>
       </c>
-      <c r="B53" s="5" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="C53" s="7">
+      <c r="B53" s="6" t="n">
+        <v>43.13</v>
+      </c>
+      <c r="C53" s="8">
         <f>LN(B53-30)</f>
         <v/>
       </c>
@@ -1903,10 +1904,10 @@
       <c r="A54" s="5" t="n">
         <v>1440</v>
       </c>
-      <c r="B54" s="5" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="C54" s="7">
+      <c r="B54" s="6" t="n">
+        <v>42.79</v>
+      </c>
+      <c r="C54" s="8">
         <f>LN(B54-30)</f>
         <v/>
       </c>
@@ -1915,10 +1916,10 @@
       <c r="A55" s="5" t="n">
         <v>1470</v>
       </c>
-      <c r="B55" s="5" t="n">
-        <v>42.39</v>
-      </c>
-      <c r="C55" s="7">
+      <c r="B55" s="6" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="C55" s="8">
         <f>LN(B55-30)</f>
         <v/>
       </c>
@@ -1927,10 +1928,10 @@
       <c r="A56" s="5" t="n">
         <v>1500</v>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="8">
         <f>LN(B56-30)</f>
         <v/>
       </c>
@@ -1939,10 +1940,10 @@
       <c r="A57" s="5" t="n">
         <v>1530</v>
       </c>
-      <c r="B57" s="5" t="n">
-        <v>41.55</v>
-      </c>
-      <c r="C57" s="7">
+      <c r="B57" s="6" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="C57" s="8">
         <f>LN(B57-30)</f>
         <v/>
       </c>
@@ -1951,10 +1952,10 @@
       <c r="A58" s="5" t="n">
         <v>1560</v>
       </c>
-      <c r="B58" s="5" t="n">
-        <v>41.23</v>
-      </c>
-      <c r="C58" s="7">
+      <c r="B58" s="6" t="n">
+        <v>41.19</v>
+      </c>
+      <c r="C58" s="8">
         <f>LN(B58-30)</f>
         <v/>
       </c>
@@ -1963,10 +1964,10 @@
       <c r="A59" s="5" t="n">
         <v>1590</v>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="6" t="n">
         <v>40.88</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="8">
         <f>LN(B59-30)</f>
         <v/>
       </c>
@@ -1975,10 +1976,10 @@
       <c r="A60" s="5" t="n">
         <v>1620</v>
       </c>
-      <c r="B60" s="5" t="n">
-        <v>40.62</v>
-      </c>
-      <c r="C60" s="7">
+      <c r="B60" s="6" t="n">
+        <v>40.54</v>
+      </c>
+      <c r="C60" s="8">
         <f>LN(B60-30)</f>
         <v/>
       </c>
@@ -1987,10 +1988,10 @@
       <c r="A61" s="5" t="n">
         <v>1650</v>
       </c>
-      <c r="B61" s="5" t="n">
-        <v>40.32</v>
-      </c>
-      <c r="C61" s="7">
+      <c r="B61" s="6" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="C61" s="8">
         <f>LN(B61-30)</f>
         <v/>
       </c>
@@ -1999,10 +2000,10 @@
       <c r="A62" s="5" t="n">
         <v>1680</v>
       </c>
-      <c r="B62" s="5" t="n">
-        <v>39.94</v>
-      </c>
-      <c r="C62" s="7">
+      <c r="B62" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="C62" s="8">
         <f>LN(B62-30)</f>
         <v/>
       </c>
@@ -2011,10 +2012,10 @@
       <c r="A63" s="5" t="n">
         <v>1710</v>
       </c>
-      <c r="B63" s="5" t="n">
-        <v>39.59</v>
-      </c>
-      <c r="C63" s="7">
+      <c r="B63" s="6" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="C63" s="8">
         <f>LN(B63-30)</f>
         <v/>
       </c>
@@ -2023,10 +2024,10 @@
       <c r="A64" s="5" t="n">
         <v>1740</v>
       </c>
-      <c r="B64" s="5" t="n">
-        <v>39.4</v>
-      </c>
-      <c r="C64" s="7">
+      <c r="B64" s="6" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="C64" s="8">
         <f>LN(B64-30)</f>
         <v/>
       </c>
@@ -2035,10 +2036,10 @@
       <c r="A65" s="5" t="n">
         <v>1770</v>
       </c>
-      <c r="B65" s="5" t="n">
-        <v>39.13</v>
-      </c>
-      <c r="C65" s="7">
+      <c r="B65" s="6" t="n">
+        <v>39.11</v>
+      </c>
+      <c r="C65" s="8">
         <f>LN(B65-30)</f>
         <v/>
       </c>
@@ -2047,10 +2048,10 @@
       <c r="A66" s="5" t="n">
         <v>1800</v>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="6" t="n">
         <v>38.85</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="8">
         <f>LN(B66-30)</f>
         <v/>
       </c>
